--- a/CWatM_settings/cwatm_settings.xlsx
+++ b/CWatM_settings/cwatm_settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\FUSE\CWatM_settings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaumot\Documents\GitHub\FUSE\CWatM_settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E22BE3-7625-4C0F-994E-B6B7837F5C3E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B2385E-5FDF-49D2-8F3B-F5CA5DC3A831}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1272" yWindow="-96" windowWidth="21864" windowHeight="13152" xr2:uid="{3B47940C-5F20-42D1-80D0-733DA86DBAA8}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{3B47940C-5F20-42D1-80D0-733DA86DBAA8}"/>
   </bookViews>
   <sheets>
     <sheet name="CWatM_input" sheetId="3" r:id="rId1"/>
@@ -25,9 +25,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="568">
   <si>
     <t>PathRoot</t>
   </si>
@@ -1727,13 +1725,25 @@
   </si>
   <si>
     <t xml:space="preserve"> $(FILE_PATHS:PathMaps)/metaNetcdf.xml</t>
+  </si>
+  <si>
+    <t>C:/Users/guillaumot/Documents/GitHub/FUSE</t>
+  </si>
+  <si>
+    <t>C:/Users/guillaumot/Documents/Local_CWATM_output</t>
+  </si>
+  <si>
+    <t>modflowtotalSoilThickness</t>
+  </si>
+  <si>
+    <t>OUT_MAP_totalend</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1781,6 +1791,11 @@
       <color rgb="FF333333"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFA9B7C6"/>
+      <name val="JetBrains Mono"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2033,7 +2048,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2073,6 +2087,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2389,704 +2406,708 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62071E38-783F-4567-BA81-7A39AFFE25E7}">
   <dimension ref="A1:B203"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.3125" style="24" customWidth="1"/>
     <col min="2" max="2" width="47.734375" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="8.83984375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:2" ht="14.7" thickBot="1">
+      <c r="A1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2">
       <c r="A2" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="37" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2">
       <c r="A3" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2">
       <c r="A4" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="39">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="38">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="27" t="s">
         <v>407</v>
       </c>
-      <c r="B5" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
         <v>557</v>
       </c>
-      <c r="B6" s="40" t="b">
+      <c r="B6" s="39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2">
       <c r="A7" s="27" t="s">
         <v>544</v>
       </c>
-      <c r="B7" s="40"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="39"/>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="27" t="s">
         <v>517</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="39" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="42" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="43" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="44" t="s">
+      <c r="B9" s="42" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="14.7" thickBot="1">
+      <c r="A10" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="33" t="s">
+      <c r="B10" s="44" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="33" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="33" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="33" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="35" t="b">
+      <c r="B13" s="34" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="33" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="34" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="33" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="34" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="33" t="s">
+    <row r="17" spans="1:2">
+      <c r="A17" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="35" t="b">
+      <c r="B17" s="34" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="33" t="s">
+    <row r="18" spans="1:2">
+      <c r="A18" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="34" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="36" t="s">
+    <row r="19" spans="1:2" ht="14.7" thickBot="1">
+      <c r="A19" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="36" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="31"/>
-      <c r="B20" s="30"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2">
+      <c r="A20" s="45" t="s">
+        <v>567</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="25"/>
       <c r="B21" s="25"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2">
       <c r="A22" s="25"/>
       <c r="B22" s="25"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2">
       <c r="A27" s="25"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2">
       <c r="A28" s="25"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2">
       <c r="A29" s="25"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2">
       <c r="A30" s="25"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2">
       <c r="A31" s="25"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2">
       <c r="A32" s="25"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:1">
       <c r="A33" s="25"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:1">
       <c r="A34" s="25"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:1">
       <c r="A35" s="25"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:1">
       <c r="A36" s="25"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:1">
       <c r="A37" s="25"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:1">
       <c r="A38" s="25"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:1">
       <c r="A39" s="25"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:1">
       <c r="A40" s="25"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:1">
       <c r="A41" s="25"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:1">
       <c r="A42" s="25"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:1">
       <c r="A43" s="25"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:1">
       <c r="A44" s="25"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:1">
       <c r="A45" s="25"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:1">
       <c r="A46" s="25"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:1">
       <c r="A47" s="25"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:1">
       <c r="A48" s="25"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:1">
       <c r="A49" s="25"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:1">
       <c r="A50" s="25"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:1">
       <c r="A51" s="25"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:1">
       <c r="A52" s="25"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:1">
       <c r="A53" s="25"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:1">
       <c r="A54" s="25"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:1">
       <c r="A55" s="25"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:1">
       <c r="A56" s="25"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:1">
       <c r="A57" s="25"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:1">
       <c r="A58" s="25"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:1">
       <c r="A59" s="25"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:1">
       <c r="A60" s="25"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:1">
       <c r="A61" s="25"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:1">
       <c r="A62" s="25"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:1">
       <c r="A63" s="25"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:1">
       <c r="A64" s="25"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:1">
       <c r="A65" s="25"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:1">
       <c r="A66" s="25"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:1">
       <c r="A67" s="25"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:1">
       <c r="A68" s="25"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:1">
       <c r="A69" s="25"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:1">
       <c r="A70" s="25"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:1">
       <c r="A71" s="25"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:1">
       <c r="A72" s="25"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:1">
       <c r="A73" s="25"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:1">
       <c r="A74" s="25"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:1">
       <c r="A75" s="25"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:1">
       <c r="A76" s="25"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:1">
       <c r="A77" s="25"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:1">
       <c r="A78" s="25"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:1">
       <c r="A79" s="25"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:1">
       <c r="A80" s="25"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:1">
       <c r="A81" s="25"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:1">
       <c r="A82" s="25"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:1">
       <c r="A83" s="25"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:1">
       <c r="A84" s="25"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:1">
       <c r="A85" s="25"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:1">
       <c r="A86" s="25"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:1">
       <c r="A87" s="25"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:1">
       <c r="A88" s="25"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:1">
       <c r="A89" s="25"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:1">
       <c r="A90" s="25"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:1">
       <c r="A91" s="25"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:1">
       <c r="A92" s="25"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:1">
       <c r="A93" s="25"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:1">
       <c r="A94" s="25"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:1">
       <c r="A95" s="25"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:1">
       <c r="A96" s="25"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:1">
       <c r="A97" s="25"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:1">
       <c r="A98" s="25"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:1">
       <c r="A99" s="25"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:1">
       <c r="A100" s="25"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:1">
       <c r="A101" s="25"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:1">
       <c r="A102" s="25"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:1">
       <c r="A103" s="25"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:1">
       <c r="A104" s="25"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:1">
       <c r="A105" s="25"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:1">
       <c r="A106" s="25"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:1">
       <c r="A107" s="25"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:1">
       <c r="A108" s="25"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:1">
       <c r="A109" s="25"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:1">
       <c r="A110" s="25"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:1">
       <c r="A111" s="25"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:1">
       <c r="A112" s="25"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:1">
       <c r="A113" s="25"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:1">
       <c r="A114" s="25"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:1">
       <c r="A115" s="25"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:1">
       <c r="A116" s="25"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:1">
       <c r="A117" s="25"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:1">
       <c r="A118" s="25"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:1">
       <c r="A119" s="25"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:1">
       <c r="A120" s="25"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:1">
       <c r="A121" s="25"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:1">
       <c r="A122" s="25"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:1">
       <c r="A123" s="25"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:1">
       <c r="A124" s="25"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:1">
       <c r="A125" s="25"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:1">
       <c r="A126" s="25"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:1">
       <c r="A127" s="25"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:1">
       <c r="A128" s="25"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:1">
       <c r="A129" s="25"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:1">
       <c r="A130" s="25"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:1">
       <c r="A131" s="25"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:1">
       <c r="A132" s="25"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:1">
       <c r="A133" s="25"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:1">
       <c r="A134" s="25"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:1">
       <c r="A135" s="25"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:1">
       <c r="A136" s="25"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:1">
       <c r="A137" s="25"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:1">
       <c r="A138" s="25"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:1">
       <c r="A139" s="25"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:1">
       <c r="A140" s="25"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:1">
       <c r="A141" s="25"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:1">
       <c r="A142" s="25"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:1">
       <c r="A143" s="25"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:1">
       <c r="A144" s="25"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:1">
       <c r="A145" s="25"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:1">
       <c r="A146" s="25"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:1">
       <c r="A147" s="25"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:1">
       <c r="A148" s="25"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:1">
       <c r="A149" s="25"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:1">
       <c r="A150" s="25"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:1">
       <c r="A151" s="25"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:1">
       <c r="A152" s="25"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:1">
       <c r="A153" s="25"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:1">
       <c r="A154" s="25"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:1">
       <c r="A155" s="25"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:1">
       <c r="A156" s="25"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:1">
       <c r="A157" s="25"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:1">
       <c r="A158" s="25"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:1">
       <c r="A159" s="25"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:1">
       <c r="A160" s="25"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:1">
       <c r="A161" s="25"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:1">
       <c r="A162" s="25"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:1">
       <c r="A163" s="25"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:1">
       <c r="A164" s="25"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:1">
       <c r="A165" s="25"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:1">
       <c r="A166" s="25"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:1">
       <c r="A167" s="25"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:1">
       <c r="A168" s="25"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:1">
       <c r="A169" s="25"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:1">
       <c r="A170" s="25"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:1">
       <c r="A171" s="25"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:1">
       <c r="A172" s="25"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:1">
       <c r="A173" s="25"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:1">
       <c r="A174" s="25"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:1">
       <c r="A175" s="25"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:1">
       <c r="A176" s="25"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:1">
       <c r="A177" s="25"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:1">
       <c r="A178" s="25"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:1">
       <c r="A179" s="25"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:1">
       <c r="A180" s="25"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:1">
       <c r="A181" s="25"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:1">
       <c r="A182" s="25"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:1">
       <c r="A183" s="25"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:1">
       <c r="A184" s="25"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:1">
       <c r="A185" s="25"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:1">
       <c r="A186" s="25"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:1">
       <c r="A187" s="25"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:1">
       <c r="A188" s="25"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:1">
       <c r="A189" s="25"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:1">
       <c r="A190" s="25"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:1">
       <c r="A191" s="25"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:1">
       <c r="A192" s="25"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:1">
       <c r="A193" s="25"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:1">
       <c r="A194" s="25"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:1">
       <c r="A195" s="25"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:1">
       <c r="A196" s="25"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:1">
       <c r="A197" s="25"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:1">
       <c r="A198" s="25"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:1">
       <c r="A199" s="25"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:1">
       <c r="A200" s="25"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:1">
       <c r="A201" s="25"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:1">
       <c r="A202" s="25"/>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:1">
       <c r="A203" s="25"/>
     </row>
   </sheetData>
@@ -3098,7 +3119,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A0B17ED-365F-42A2-8A56-1051B9FEC7F3}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.9" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="25.578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="76.15625" style="2" bestFit="1" customWidth="1"/>
@@ -3107,7 +3128,7 @@
     <col min="5" max="16384" width="9.15625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -3121,7 +3142,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3135,7 +3156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -3149,7 +3170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3163,7 +3184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -3177,7 +3198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -3191,7 +3212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -3205,7 +3226,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
@@ -3219,7 +3240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -3233,7 +3254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
@@ -3247,7 +3268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -3261,7 +3282,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:4">
       <c r="A12" s="6" t="s">
         <v>17</v>
       </c>
@@ -3275,7 +3296,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
         <v>30</v>
       </c>
@@ -3286,7 +3307,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
         <v>32</v>
       </c>
@@ -3297,7 +3318,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -3308,7 +3329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -3316,7 +3337,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -3327,17 +3348,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" ht="14.4">
       <c r="A22" s="7" t="s">
         <v>544</v>
       </c>
@@ -3345,12 +3366,12 @@
         <v>548</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:4">
       <c r="B23" s="2" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" ht="14.4">
       <c r="A25" s="2" t="s">
         <v>554</v>
       </c>
@@ -3358,7 +3379,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" ht="14.4">
       <c r="A29" s="2" t="s">
         <v>556</v>
       </c>
@@ -3375,7 +3396,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F68B577-1ED3-4341-9ED6-7148A85D6559}">
   <dimension ref="A1:G501"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.83984375" style="8" bestFit="1" customWidth="1"/>
@@ -3386,7 +3407,7 @@
     <col min="7" max="7" width="16.578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7">
       <c r="A1" s="11" t="s">
         <v>519</v>
       </c>
@@ -3409,7 +3430,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7">
       <c r="A2" s="7" t="s">
         <v>46</v>
       </c>
@@ -3420,7 +3441,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7">
       <c r="A3" s="7" t="s">
         <v>46</v>
       </c>
@@ -3431,7 +3452,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7">
       <c r="A4" s="7" t="s">
         <v>46</v>
       </c>
@@ -3442,7 +3463,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" s="17" customFormat="1">
       <c r="A5" s="15" t="s">
         <v>46</v>
       </c>
@@ -3456,7 +3477,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
         <v>46</v>
       </c>
@@ -3467,7 +3488,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7">
       <c r="A7" s="7" t="s">
         <v>46</v>
       </c>
@@ -3478,7 +3499,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
         <v>46</v>
       </c>
@@ -3489,7 +3510,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7">
       <c r="A9" s="7" t="s">
         <v>46</v>
       </c>
@@ -3500,7 +3521,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
         <v>46</v>
       </c>
@@ -3511,7 +3532,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
         <v>46</v>
       </c>
@@ -3522,7 +3543,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7">
       <c r="A12" s="7" t="s">
         <v>46</v>
       </c>
@@ -3533,7 +3554,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7">
       <c r="A13" s="7" t="s">
         <v>46</v>
       </c>
@@ -3544,7 +3565,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7">
       <c r="A14" s="7" t="s">
         <v>46</v>
       </c>
@@ -3555,7 +3576,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7">
       <c r="A15" s="7" t="s">
         <v>46</v>
       </c>
@@ -3566,7 +3587,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -3577,7 +3598,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -3588,7 +3609,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7">
       <c r="A18" s="7" t="s">
         <v>46</v>
       </c>
@@ -3599,7 +3620,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7">
       <c r="A19" s="7" t="s">
         <v>46</v>
       </c>
@@ -3610,7 +3631,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7">
       <c r="A20" s="7" t="s">
         <v>46</v>
       </c>
@@ -3621,7 +3642,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7">
       <c r="A21" s="7" t="s">
         <v>46</v>
       </c>
@@ -3632,7 +3653,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7">
       <c r="A22" s="7" t="s">
         <v>46</v>
       </c>
@@ -3643,7 +3664,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7">
       <c r="A23" s="7" t="s">
         <v>46</v>
       </c>
@@ -3654,7 +3675,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:7">
       <c r="A24" s="7" t="s">
         <v>46</v>
       </c>
@@ -3668,7 +3689,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7">
       <c r="A25" s="7" t="s">
         <v>46</v>
       </c>
@@ -3682,7 +3703,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:7">
       <c r="A26" s="7" t="s">
         <v>46</v>
       </c>
@@ -3696,7 +3717,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:7">
       <c r="A27" s="7" t="s">
         <v>46</v>
       </c>
@@ -3707,7 +3728,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:7" s="23" customFormat="1">
       <c r="A28" s="21" t="s">
         <v>46</v>
       </c>
@@ -3718,7 +3739,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:7">
       <c r="A29" s="7" t="s">
         <v>47</v>
       </c>
@@ -3729,7 +3750,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:7">
       <c r="A30" s="7" t="s">
         <v>47</v>
       </c>
@@ -3740,7 +3761,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:7">
       <c r="A31" s="7" t="s">
         <v>47</v>
       </c>
@@ -3751,7 +3772,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7">
       <c r="A32" s="7" t="s">
         <v>47</v>
       </c>
@@ -3762,7 +3783,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
         <v>48</v>
       </c>
@@ -3773,7 +3794,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
         <v>48</v>
       </c>
@@ -3784,7 +3805,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
         <v>48</v>
       </c>
@@ -3795,7 +3816,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
         <v>49</v>
       </c>
@@ -3806,7 +3827,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:3">
       <c r="A37" s="7" t="s">
         <v>49</v>
       </c>
@@ -3817,7 +3838,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:3">
       <c r="A38" s="7" t="s">
         <v>49</v>
       </c>
@@ -3828,7 +3849,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:3">
       <c r="A39" s="7" t="s">
         <v>50</v>
       </c>
@@ -3839,7 +3860,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:3">
       <c r="A40" s="7" t="s">
         <v>50</v>
       </c>
@@ -3850,7 +3871,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:3">
       <c r="A41" s="7" t="s">
         <v>50</v>
       </c>
@@ -3861,7 +3882,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:3">
       <c r="A42" s="7" t="s">
         <v>51</v>
       </c>
@@ -3872,7 +3893,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:3">
       <c r="A43" s="7" t="s">
         <v>51</v>
       </c>
@@ -3883,7 +3904,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:3">
       <c r="A44" s="7" t="s">
         <v>51</v>
       </c>
@@ -3894,7 +3915,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:3">
       <c r="A45" s="7" t="s">
         <v>51</v>
       </c>
@@ -3905,7 +3926,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:3">
       <c r="A46" s="7" t="s">
         <v>51</v>
       </c>
@@ -3916,7 +3937,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:3">
       <c r="A47" s="7" t="s">
         <v>52</v>
       </c>
@@ -3927,7 +3948,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:3">
       <c r="A48" s="7" t="s">
         <v>52</v>
       </c>
@@ -3938,7 +3959,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:3">
       <c r="A49" s="7" t="s">
         <v>52</v>
       </c>
@@ -3949,7 +3970,7 @@
         <v>1.6724858092486401</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:3">
       <c r="A50" s="7" t="s">
         <v>52</v>
       </c>
@@ -3960,7 +3981,7 @@
         <v>1.4522320737216501</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:3">
       <c r="A51" s="7" t="s">
         <v>52</v>
       </c>
@@ -3971,7 +3992,7 @@
         <v>3.9792416752925099</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:3">
       <c r="A52" s="7" t="s">
         <v>52</v>
       </c>
@@ -3982,7 +4003,7 @@
         <v>0.172979234117665</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3">
       <c r="A53" s="7" t="s">
         <v>52</v>
       </c>
@@ -3993,7 +4014,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:3">
       <c r="A54" s="7" t="s">
         <v>52</v>
       </c>
@@ -4004,7 +4025,7 @@
         <v>5.08489365888276</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:3">
       <c r="A55" s="7" t="s">
         <v>52</v>
       </c>
@@ -4015,7 +4036,7 @@
         <v>2.3669378692197398</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3">
       <c r="A56" s="7" t="s">
         <v>52</v>
       </c>
@@ -4026,7 +4047,7 @@
         <v>4.4825774640604799</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:3">
       <c r="A57" s="7" t="s">
         <v>52</v>
       </c>
@@ -4037,7 +4058,7 @@
         <v>0.645563228322237</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:3">
       <c r="A58" s="7" t="s">
         <v>52</v>
       </c>
@@ -4048,7 +4069,7 @@
         <v>1.8965519432548701</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:3">
       <c r="A59" s="7" t="s">
         <v>52</v>
       </c>
@@ -4059,7 +4080,7 @@
         <v>1.66966067574903</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:3">
       <c r="A60" s="7" t="s">
         <v>52</v>
       </c>
@@ -4070,7 +4091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:3">
       <c r="A61" s="7" t="s">
         <v>52</v>
       </c>
@@ -4081,7 +4102,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:3">
       <c r="A62" s="7" t="s">
         <v>53</v>
       </c>
@@ -4092,7 +4113,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="63" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:3" s="17" customFormat="1">
       <c r="A63" s="15" t="s">
         <v>53</v>
       </c>
@@ -4103,7 +4124,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="64" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:3" s="17" customFormat="1">
       <c r="A64" s="15" t="s">
         <v>53</v>
       </c>
@@ -4114,7 +4135,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:3">
       <c r="A65" s="7" t="s">
         <v>53</v>
       </c>
@@ -4125,7 +4146,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:3">
       <c r="A66" s="7" t="s">
         <v>53</v>
       </c>
@@ -4136,7 +4157,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:3">
       <c r="A67" s="7" t="s">
         <v>53</v>
       </c>
@@ -4147,7 +4168,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:3">
       <c r="A68" s="7" t="s">
         <v>54</v>
       </c>
@@ -4158,7 +4179,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:3">
       <c r="A69" s="7" t="s">
         <v>54</v>
       </c>
@@ -4169,7 +4190,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:3">
       <c r="A70" s="7" t="s">
         <v>54</v>
       </c>
@@ -4180,7 +4201,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:3">
       <c r="A71" s="7" t="s">
         <v>54</v>
       </c>
@@ -4191,7 +4212,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:3">
       <c r="A72" s="7" t="s">
         <v>54</v>
       </c>
@@ -4202,7 +4223,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:3">
       <c r="A73" s="7" t="s">
         <v>54</v>
       </c>
@@ -4213,7 +4234,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:3">
       <c r="A74" s="7" t="s">
         <v>54</v>
       </c>
@@ -4224,7 +4245,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:3">
       <c r="A75" s="7" t="s">
         <v>54</v>
       </c>
@@ -4235,7 +4256,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:3">
       <c r="A76" s="7" t="s">
         <v>54</v>
       </c>
@@ -4246,7 +4267,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:3">
       <c r="A77" s="7" t="s">
         <v>54</v>
       </c>
@@ -4257,7 +4278,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:3">
       <c r="A78" s="7" t="s">
         <v>54</v>
       </c>
@@ -4268,7 +4289,7 @@
         <v>86.4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:3">
       <c r="A79" s="7" t="s">
         <v>54</v>
       </c>
@@ -4279,7 +4300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:3">
       <c r="A80" s="7" t="s">
         <v>55</v>
       </c>
@@ -4290,7 +4311,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:3">
       <c r="A81" s="7" t="s">
         <v>55</v>
       </c>
@@ -4301,7 +4322,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:3">
       <c r="A82" s="7" t="s">
         <v>55</v>
       </c>
@@ -4312,7 +4333,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:3">
       <c r="A83" s="7" t="s">
         <v>55</v>
       </c>
@@ -4323,7 +4344,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:3">
       <c r="A84" s="7" t="s">
         <v>55</v>
       </c>
@@ -4334,7 +4355,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:3">
       <c r="A85" s="7" t="s">
         <v>55</v>
       </c>
@@ -4345,7 +4366,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:3">
       <c r="A86" s="7" t="s">
         <v>55</v>
       </c>
@@ -4356,7 +4377,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:3">
       <c r="A87" s="7" t="s">
         <v>55</v>
       </c>
@@ -4367,7 +4388,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:3">
       <c r="A88" s="7" t="s">
         <v>55</v>
       </c>
@@ -4378,7 +4399,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:3">
       <c r="A89" s="7" t="s">
         <v>55</v>
       </c>
@@ -4389,7 +4410,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:3">
       <c r="A90" s="7" t="s">
         <v>55</v>
       </c>
@@ -4400,7 +4421,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:3">
       <c r="A91" s="7" t="s">
         <v>55</v>
       </c>
@@ -4411,7 +4432,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:3">
       <c r="A92" s="7" t="s">
         <v>55</v>
       </c>
@@ -4422,7 +4443,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:3">
       <c r="A93" s="7" t="s">
         <v>56</v>
       </c>
@@ -4433,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:3">
       <c r="A94" s="7" t="s">
         <v>56</v>
       </c>
@@ -4444,7 +4465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:3">
       <c r="A95" s="7" t="s">
         <v>56</v>
       </c>
@@ -4455,7 +4476,7 @@
         <v>6.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:3">
       <c r="A96" s="7" t="s">
         <v>56</v>
       </c>
@@ -4466,7 +4487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:3">
       <c r="A97" s="7" t="s">
         <v>56</v>
       </c>
@@ -4477,7 +4498,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:3">
       <c r="A98" s="7" t="s">
         <v>56</v>
       </c>
@@ -4488,7 +4509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:3">
       <c r="A99" s="7" t="s">
         <v>56</v>
       </c>
@@ -4499,7 +4520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:3">
       <c r="A100" s="7" t="s">
         <v>56</v>
       </c>
@@ -4510,7 +4531,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:3">
       <c r="A101" s="7" t="s">
         <v>57</v>
       </c>
@@ -4521,7 +4542,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:3">
       <c r="A102" s="7" t="s">
         <v>57</v>
       </c>
@@ -4532,7 +4553,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:3">
       <c r="A103" s="7" t="s">
         <v>57</v>
       </c>
@@ -4543,7 +4564,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:3">
       <c r="A104" s="7" t="s">
         <v>57</v>
       </c>
@@ -4554,7 +4575,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:3">
       <c r="A105" s="7" t="s">
         <v>58</v>
       </c>
@@ -4565,7 +4586,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:3">
       <c r="A106" s="7" t="s">
         <v>59</v>
       </c>
@@ -4576,7 +4597,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:3">
       <c r="A107" s="7" t="s">
         <v>59</v>
       </c>
@@ -4587,7 +4608,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:3">
       <c r="A108" s="7" t="s">
         <v>59</v>
       </c>
@@ -4598,7 +4619,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:3">
       <c r="A109" s="7" t="s">
         <v>59</v>
       </c>
@@ -4609,7 +4630,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:3">
       <c r="A110" s="7" t="s">
         <v>59</v>
       </c>
@@ -4620,7 +4641,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:3">
       <c r="A111" s="7" t="s">
         <v>59</v>
       </c>
@@ -4631,7 +4652,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:3">
       <c r="A112" s="7" t="s">
         <v>59</v>
       </c>
@@ -4642,7 +4663,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:3">
       <c r="A113" s="7" t="s">
         <v>59</v>
       </c>
@@ -4653,7 +4674,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:3">
       <c r="A114" s="7" t="s">
         <v>59</v>
       </c>
@@ -4664,7 +4685,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:3">
       <c r="A115" s="7" t="s">
         <v>59</v>
       </c>
@@ -4675,7 +4696,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:3">
       <c r="A116" s="7" t="s">
         <v>59</v>
       </c>
@@ -4686,7 +4707,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:3">
       <c r="A117" s="7" t="s">
         <v>59</v>
       </c>
@@ -4697,7 +4718,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:3">
       <c r="A118" s="7" t="s">
         <v>59</v>
       </c>
@@ -4708,7 +4729,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:3">
       <c r="A119" s="7" t="s">
         <v>59</v>
       </c>
@@ -4719,7 +4740,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:3">
       <c r="A120" s="7" t="s">
         <v>59</v>
       </c>
@@ -4730,7 +4751,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:3">
       <c r="A121" s="7" t="s">
         <v>59</v>
       </c>
@@ -4741,7 +4762,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:3">
       <c r="A122" s="7" t="s">
         <v>59</v>
       </c>
@@ -4752,7 +4773,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:3">
       <c r="A123" s="7" t="s">
         <v>59</v>
       </c>
@@ -4763,7 +4784,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:3">
       <c r="A124" s="7" t="s">
         <v>59</v>
       </c>
@@ -4774,7 +4795,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:3">
       <c r="A125" s="7" t="s">
         <v>59</v>
       </c>
@@ -4785,7 +4806,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:3">
       <c r="A126" s="7" t="s">
         <v>59</v>
       </c>
@@ -4796,7 +4817,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:3">
       <c r="A127" s="7" t="s">
         <v>59</v>
       </c>
@@ -4807,7 +4828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:3">
       <c r="A128" s="7" t="s">
         <v>59</v>
       </c>
@@ -4818,7 +4839,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:3">
       <c r="A129" s="7" t="s">
         <v>59</v>
       </c>
@@ -4829,7 +4850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:3">
       <c r="A130" s="7" t="s">
         <v>59</v>
       </c>
@@ -4840,7 +4861,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:3">
       <c r="A131" s="7" t="s">
         <v>59</v>
       </c>
@@ -4851,7 +4872,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:3">
       <c r="A132" s="7" t="s">
         <v>60</v>
       </c>
@@ -4862,7 +4883,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:3">
       <c r="A133" s="7" t="s">
         <v>60</v>
       </c>
@@ -4873,7 +4894,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:3">
       <c r="A134" s="7" t="s">
         <v>60</v>
       </c>
@@ -4884,7 +4905,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:3">
       <c r="A135" s="7" t="s">
         <v>60</v>
       </c>
@@ -4895,7 +4916,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:3">
       <c r="A136" s="7" t="s">
         <v>60</v>
       </c>
@@ -4906,7 +4927,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:3">
       <c r="A137" s="7" t="s">
         <v>60</v>
       </c>
@@ -4917,7 +4938,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:3">
       <c r="A138" s="7" t="s">
         <v>60</v>
       </c>
@@ -4928,7 +4949,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:3">
       <c r="A139" s="7" t="s">
         <v>60</v>
       </c>
@@ -4939,7 +4960,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:3">
       <c r="A140" s="7" t="s">
         <v>60</v>
       </c>
@@ -4950,7 +4971,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:3">
       <c r="A141" s="7" t="s">
         <v>60</v>
       </c>
@@ -4961,7 +4982,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:3">
       <c r="A142" s="7" t="s">
         <v>60</v>
       </c>
@@ -4972,7 +4993,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:3">
       <c r="A143" s="7" t="s">
         <v>60</v>
       </c>
@@ -4983,7 +5004,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:3">
       <c r="A144" s="7" t="s">
         <v>60</v>
       </c>
@@ -4994,7 +5015,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:3">
       <c r="A145" s="7" t="s">
         <v>61</v>
       </c>
@@ -5005,7 +5026,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:3">
       <c r="A146" s="7" t="s">
         <v>61</v>
       </c>
@@ -5016,7 +5037,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:3">
       <c r="A147" s="7" t="s">
         <v>61</v>
       </c>
@@ -5027,7 +5048,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:3">
       <c r="A148" s="7" t="s">
         <v>61</v>
       </c>
@@ -5038,7 +5059,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:3">
       <c r="A149" s="7" t="s">
         <v>61</v>
       </c>
@@ -5049,7 +5070,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:3">
       <c r="A150" s="7" t="s">
         <v>61</v>
       </c>
@@ -5060,7 +5081,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:3">
       <c r="A151" s="7" t="s">
         <v>61</v>
       </c>
@@ -5071,7 +5092,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:3">
       <c r="A152" s="7" t="s">
         <v>61</v>
       </c>
@@ -5082,7 +5103,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:3">
       <c r="A153" s="7" t="s">
         <v>61</v>
       </c>
@@ -5093,7 +5114,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:3">
       <c r="A154" s="7" t="s">
         <v>61</v>
       </c>
@@ -5104,7 +5125,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:3">
       <c r="A155" s="7" t="s">
         <v>61</v>
       </c>
@@ -5115,7 +5136,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:3">
       <c r="A156" s="7" t="s">
         <v>61</v>
       </c>
@@ -5126,7 +5147,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:3">
       <c r="A157" s="7" t="s">
         <v>61</v>
       </c>
@@ -5137,7 +5158,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:3">
       <c r="A158" s="7" t="s">
         <v>61</v>
       </c>
@@ -5148,7 +5169,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:3">
       <c r="A159" s="7" t="s">
         <v>61</v>
       </c>
@@ -5159,7 +5180,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:3">
       <c r="A160" s="7" t="s">
         <v>61</v>
       </c>
@@ -5170,7 +5191,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:3">
       <c r="A161" s="7" t="s">
         <v>61</v>
       </c>
@@ -5181,7 +5202,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:3">
       <c r="A162" s="7" t="s">
         <v>61</v>
       </c>
@@ -5192,7 +5213,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:3">
       <c r="A163" s="7" t="s">
         <v>61</v>
       </c>
@@ -5203,7 +5224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:3">
       <c r="A164" s="7" t="s">
         <v>61</v>
       </c>
@@ -5214,7 +5235,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:3">
       <c r="A165" s="7" t="s">
         <v>61</v>
       </c>
@@ -5225,7 +5246,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:3">
       <c r="A166" s="7" t="s">
         <v>61</v>
       </c>
@@ -5236,7 +5257,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:3">
       <c r="A167" s="7" t="s">
         <v>61</v>
       </c>
@@ -5247,7 +5268,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:3">
       <c r="A168" s="7" t="s">
         <v>61</v>
       </c>
@@ -5258,7 +5279,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:3">
       <c r="A169" s="7" t="s">
         <v>62</v>
       </c>
@@ -5269,7 +5290,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:3">
       <c r="A170" s="7" t="s">
         <v>62</v>
       </c>
@@ -5280,7 +5301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:3">
       <c r="A171" s="7" t="s">
         <v>62</v>
       </c>
@@ -5291,7 +5312,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:3">
       <c r="A172" s="7" t="s">
         <v>62</v>
       </c>
@@ -5302,7 +5323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:3">
       <c r="A173" s="7" t="s">
         <v>62</v>
       </c>
@@ -5313,7 +5334,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:3">
       <c r="A174" s="7" t="s">
         <v>62</v>
       </c>
@@ -5324,7 +5345,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:3">
       <c r="A175" s="7" t="s">
         <v>62</v>
       </c>
@@ -5335,7 +5356,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:3">
       <c r="A176" s="7" t="s">
         <v>62</v>
       </c>
@@ -5346,7 +5367,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:3">
       <c r="A177" s="7" t="s">
         <v>62</v>
       </c>
@@ -5357,7 +5378,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:3">
       <c r="A178" s="7" t="s">
         <v>63</v>
       </c>
@@ -5368,7 +5389,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:3">
       <c r="A179" s="7" t="s">
         <v>63</v>
       </c>
@@ -5379,7 +5400,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:3">
       <c r="A180" s="7" t="s">
         <v>63</v>
       </c>
@@ -5390,7 +5411,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:3">
       <c r="A181" s="7" t="s">
         <v>63</v>
       </c>
@@ -5401,7 +5422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:3">
       <c r="A182" s="7" t="s">
         <v>63</v>
       </c>
@@ -5412,7 +5433,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:3">
       <c r="A183" s="7" t="s">
         <v>63</v>
       </c>
@@ -5423,7 +5444,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:3">
       <c r="A184" s="7" t="s">
         <v>63</v>
       </c>
@@ -5434,7 +5455,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:3">
       <c r="A185" s="7" t="s">
         <v>63</v>
       </c>
@@ -5445,7 +5466,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:3">
       <c r="A186" s="7" t="s">
         <v>63</v>
       </c>
@@ -5456,7 +5477,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:3">
       <c r="A187" s="7" t="s">
         <v>64</v>
       </c>
@@ -5467,7 +5488,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:3">
       <c r="A188" s="7" t="s">
         <v>64</v>
       </c>
@@ -5478,7 +5499,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:3">
       <c r="A189" s="7" t="s">
         <v>64</v>
       </c>
@@ -5489,7 +5510,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:3">
       <c r="A190" s="7" t="s">
         <v>64</v>
       </c>
@@ -5500,7 +5521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:3">
       <c r="A191" s="7" t="s">
         <v>64</v>
       </c>
@@ -5511,7 +5532,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:3">
       <c r="A192" s="7" t="s">
         <v>64</v>
       </c>
@@ -5522,7 +5543,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:3">
       <c r="A193" s="7" t="s">
         <v>64</v>
       </c>
@@ -5533,7 +5554,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:3">
       <c r="A194" s="7" t="s">
         <v>64</v>
       </c>
@@ -5544,7 +5565,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:3">
       <c r="A195" s="7" t="s">
         <v>65</v>
       </c>
@@ -5555,7 +5576,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:3">
       <c r="A196" s="7" t="s">
         <v>66</v>
       </c>
@@ -5566,7 +5587,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:3">
       <c r="A197" s="7" t="s">
         <v>66</v>
       </c>
@@ -5577,7 +5598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:3">
       <c r="A198" s="7" t="s">
         <v>67</v>
       </c>
@@ -5588,7 +5609,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:3">
       <c r="A199" s="7" t="s">
         <v>67</v>
       </c>
@@ -5599,7 +5620,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:3">
       <c r="A200" s="7" t="s">
         <v>67</v>
       </c>
@@ -5610,7 +5631,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:3">
       <c r="A201" s="7" t="s">
         <v>67</v>
       </c>
@@ -5621,7 +5642,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:3">
       <c r="A202" s="7" t="s">
         <v>68</v>
       </c>
@@ -5632,7 +5653,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:3">
       <c r="A203" s="7" t="s">
         <v>68</v>
       </c>
@@ -5643,7 +5664,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:3">
       <c r="A204" s="7" t="s">
         <v>68</v>
       </c>
@@ -5654,7 +5675,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:3">
       <c r="A205" s="7" t="s">
         <v>68</v>
       </c>
@@ -5665,7 +5686,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:3">
       <c r="A206" s="7" t="s">
         <v>68</v>
       </c>
@@ -5676,7 +5697,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:3">
       <c r="A207" s="7" t="s">
         <v>68</v>
       </c>
@@ -5687,7 +5708,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:3">
       <c r="A208" s="7" t="s">
         <v>68</v>
       </c>
@@ -5698,7 +5719,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:3">
       <c r="A209" s="7" t="s">
         <v>68</v>
       </c>
@@ -5709,7 +5730,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:3">
       <c r="A210" s="7" t="s">
         <v>68</v>
       </c>
@@ -5720,7 +5741,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:3">
       <c r="A211" s="7" t="s">
         <v>68</v>
       </c>
@@ -5731,7 +5752,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:3">
       <c r="A212" s="7" t="s">
         <v>68</v>
       </c>
@@ -5742,7 +5763,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:3">
       <c r="A213" s="7" t="s">
         <v>68</v>
       </c>
@@ -5753,7 +5774,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:3">
       <c r="A214" s="7" t="s">
         <v>68</v>
       </c>
@@ -5764,7 +5785,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:3">
       <c r="A215" s="7" t="s">
         <v>68</v>
       </c>
@@ -5775,7 +5796,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:3">
       <c r="A216" s="7" t="s">
         <v>68</v>
       </c>
@@ -5786,7 +5807,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:3">
       <c r="A217" s="7" t="s">
         <v>68</v>
       </c>
@@ -5797,7 +5818,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:3">
       <c r="A218" s="7" t="s">
         <v>68</v>
       </c>
@@ -5808,7 +5829,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:3">
       <c r="A219" s="7" t="s">
         <v>68</v>
       </c>
@@ -5819,7 +5840,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:3">
       <c r="A220" s="7" t="s">
         <v>68</v>
       </c>
@@ -5830,7 +5851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:3">
       <c r="A221" s="7" t="s">
         <v>68</v>
       </c>
@@ -5841,7 +5862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:3">
       <c r="A222" s="7" t="s">
         <v>68</v>
       </c>
@@ -5852,7 +5873,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:3">
       <c r="A223" s="7" t="s">
         <v>68</v>
       </c>
@@ -5863,7 +5884,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:3">
       <c r="A224" s="7" t="s">
         <v>68</v>
       </c>
@@ -5874,7 +5895,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:3">
       <c r="A225" s="7" t="s">
         <v>68</v>
       </c>
@@ -5885,7 +5906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:3">
       <c r="A226" s="7" t="s">
         <v>68</v>
       </c>
@@ -5896,7 +5917,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:3">
       <c r="A227" s="7" t="s">
         <v>68</v>
       </c>
@@ -5907,7 +5928,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:3">
       <c r="A228" s="7" t="s">
         <v>68</v>
       </c>
@@ -5918,7 +5939,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:3">
       <c r="A229" s="7" t="s">
         <v>69</v>
       </c>
@@ -5929,7 +5950,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="230" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:3" s="8" customFormat="1">
       <c r="A230" s="7" t="s">
         <v>69</v>
       </c>
@@ -5940,7 +5961,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:3">
       <c r="A231" s="7" t="s">
         <v>69</v>
       </c>
@@ -5951,7 +5972,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:3">
       <c r="A232" s="7" t="s">
         <v>69</v>
       </c>
@@ -5962,7 +5983,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:3">
       <c r="A233" s="7" t="s">
         <v>69</v>
       </c>
@@ -5973,7 +5994,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:3">
       <c r="A234" s="7" t="s">
         <v>69</v>
       </c>
@@ -5984,7 +6005,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:3">
       <c r="A235" s="7" t="s">
         <v>69</v>
       </c>
@@ -5995,7 +6016,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:3">
       <c r="A236" s="7" t="s">
         <v>69</v>
       </c>
@@ -6006,7 +6027,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:3">
       <c r="A237" s="7" t="s">
         <v>69</v>
       </c>
@@ -6017,7 +6038,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:3">
       <c r="A238" s="7" t="s">
         <v>69</v>
       </c>
@@ -6028,7 +6049,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:3">
       <c r="A239" s="7" t="s">
         <v>69</v>
       </c>
@@ -6039,7 +6060,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:3">
       <c r="A240" s="7" t="s">
         <v>69</v>
       </c>
@@ -6050,7 +6071,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:3">
       <c r="A241" s="7" t="s">
         <v>69</v>
       </c>
@@ -6061,7 +6082,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:3">
       <c r="A242" s="7" t="s">
         <v>69</v>
       </c>
@@ -6072,7 +6093,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:3">
       <c r="A243" s="7" t="s">
         <v>69</v>
       </c>
@@ -6083,7 +6104,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:3">
       <c r="A244" s="7" t="s">
         <v>69</v>
       </c>
@@ -6094,7 +6115,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:3">
       <c r="A245" s="7" t="s">
         <v>69</v>
       </c>
@@ -6105,7 +6126,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:3">
       <c r="A246" s="7" t="s">
         <v>69</v>
       </c>
@@ -6116,7 +6137,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:3">
       <c r="A247" s="7" t="s">
         <v>69</v>
       </c>
@@ -6127,7 +6148,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:3">
       <c r="A248" s="7" t="s">
         <v>69</v>
       </c>
@@ -6138,7 +6159,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:3">
       <c r="A249" s="7" t="s">
         <v>69</v>
       </c>
@@ -6149,7 +6170,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="250" spans="1:3" s="17" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:3" s="17" customFormat="1">
       <c r="A250" s="15" t="s">
         <v>69</v>
       </c>
@@ -6160,7 +6181,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:3">
       <c r="A251" s="7" t="s">
         <v>69</v>
       </c>
@@ -6171,7 +6192,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:3">
       <c r="A252" s="7" t="s">
         <v>69</v>
       </c>
@@ -6182,7 +6203,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:3">
       <c r="A253" s="7" t="s">
         <v>69</v>
       </c>
@@ -6193,7 +6214,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:3">
       <c r="A254" s="7" t="s">
         <v>70</v>
       </c>
@@ -6204,7 +6225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:3">
       <c r="A255" s="7" t="s">
         <v>70</v>
       </c>
@@ -6215,7 +6236,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:3">
       <c r="A256" s="7" t="s">
         <v>70</v>
       </c>
@@ -6226,7 +6247,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:3">
       <c r="A257" s="7" t="s">
         <v>70</v>
       </c>
@@ -6237,7 +6258,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:3">
       <c r="A258" s="7" t="s">
         <v>70</v>
       </c>
@@ -6248,7 +6269,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:3">
       <c r="A259" s="7" t="s">
         <v>70</v>
       </c>
@@ -6259,7 +6280,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:3">
       <c r="A260" s="7" t="s">
         <v>70</v>
       </c>
@@ -6270,7 +6291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:3">
       <c r="A261" s="7" t="s">
         <v>70</v>
       </c>
@@ -6281,7 +6302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:3">
       <c r="A262" s="7" t="s">
         <v>71</v>
       </c>
@@ -6292,7 +6313,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:3">
       <c r="A263" s="7" t="s">
         <v>71</v>
       </c>
@@ -6303,7 +6324,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:3">
       <c r="A264" s="7" t="s">
         <v>71</v>
       </c>
@@ -6314,7 +6335,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:3">
       <c r="A265" s="7" t="s">
         <v>71</v>
       </c>
@@ -6325,7 +6346,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:3">
       <c r="A266" s="7" t="s">
         <v>71</v>
       </c>
@@ -6336,7 +6357,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:3">
       <c r="A267" s="7" t="s">
         <v>71</v>
       </c>
@@ -6347,7 +6368,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:3">
       <c r="A268" s="7" t="s">
         <v>71</v>
       </c>
@@ -6358,7 +6379,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:3">
       <c r="A269" s="7" t="s">
         <v>71</v>
       </c>
@@ -6369,7 +6390,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:3">
       <c r="A270" s="7" t="s">
         <v>71</v>
       </c>
@@ -6380,7 +6401,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:3">
       <c r="A271" s="7" t="s">
         <v>72</v>
       </c>
@@ -6391,7 +6412,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:3">
       <c r="A272" s="7" t="s">
         <v>72</v>
       </c>
@@ -6402,7 +6423,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:3">
       <c r="A273" s="7" t="s">
         <v>72</v>
       </c>
@@ -6413,7 +6434,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:3">
       <c r="A274" s="7" t="s">
         <v>72</v>
       </c>
@@ -6424,7 +6445,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:3">
       <c r="A275" s="7" t="s">
         <v>72</v>
       </c>
@@ -6435,7 +6456,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:3">
       <c r="A276" s="7" t="s">
         <v>72</v>
       </c>
@@ -6446,7 +6467,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:3">
       <c r="A277" s="7" t="s">
         <v>72</v>
       </c>
@@ -6457,7 +6478,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:3">
       <c r="A278" s="7" t="s">
         <v>72</v>
       </c>
@@ -6468,7 +6489,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:3">
       <c r="A279" s="7" t="s">
         <v>72</v>
       </c>
@@ -6479,7 +6500,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="1:3">
       <c r="A280" s="7" t="s">
         <v>72</v>
       </c>
@@ -6490,7 +6511,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:3">
       <c r="A281" s="7" t="s">
         <v>72</v>
       </c>
@@ -6501,7 +6522,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:3">
       <c r="A282" s="7" t="s">
         <v>72</v>
       </c>
@@ -6512,7 +6533,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:3">
       <c r="A283" s="7" t="s">
         <v>72</v>
       </c>
@@ -6523,7 +6544,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:3">
       <c r="A284" s="7" t="s">
         <v>72</v>
       </c>
@@ -6534,7 +6555,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:3">
       <c r="A285" s="7" t="s">
         <v>72</v>
       </c>
@@ -6545,7 +6566,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="1:3">
       <c r="A286" s="7" t="s">
         <v>72</v>
       </c>
@@ -6556,7 +6577,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:3">
       <c r="A287" s="7" t="s">
         <v>72</v>
       </c>
@@ -6567,7 +6588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:3">
       <c r="A288" s="7" t="s">
         <v>72</v>
       </c>
@@ -6578,7 +6599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:3">
       <c r="A289" s="7" t="s">
         <v>72</v>
       </c>
@@ -6589,7 +6610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:3">
       <c r="A290" s="7" t="s">
         <v>72</v>
       </c>
@@ -6600,7 +6621,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:3">
       <c r="A291" s="7" t="s">
         <v>72</v>
       </c>
@@ -6611,7 +6632,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="1:3">
       <c r="A292" s="7" t="s">
         <v>72</v>
       </c>
@@ -6622,7 +6643,7 @@
         <v>0.94969999999999999</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="1:3">
       <c r="A293" s="7" t="s">
         <v>72</v>
       </c>
@@ -6633,7 +6654,7 @@
         <v>0.98499999999999999</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:3">
       <c r="A294" s="7" t="s">
         <v>72</v>
       </c>
@@ -6644,7 +6665,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:3">
       <c r="A295" s="7" t="s">
         <v>73</v>
       </c>
@@ -6655,7 +6676,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="1:3">
       <c r="A296" s="7" t="s">
         <v>73</v>
       </c>
@@ -6666,7 +6687,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="1:3">
       <c r="A297" s="7" t="s">
         <v>73</v>
       </c>
@@ -6677,7 +6698,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="1:3">
       <c r="A298" s="7" t="s">
         <v>74</v>
       </c>
@@ -6688,7 +6709,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="1:3">
       <c r="A299" s="7" t="s">
         <v>74</v>
       </c>
@@ -6699,7 +6720,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="1:3">
       <c r="A300" s="7" t="s">
         <v>74</v>
       </c>
@@ -6710,7 +6731,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:3">
       <c r="A301" s="7" t="s">
         <v>75</v>
       </c>
@@ -6721,7 +6742,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="1:3">
       <c r="A302" s="7" t="s">
         <v>75</v>
       </c>
@@ -6732,7 +6753,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="1:3">
       <c r="A303" s="7" t="s">
         <v>75</v>
       </c>
@@ -6743,598 +6764,598 @@
         <v>545</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="1:3">
       <c r="B304"/>
     </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="2:2">
       <c r="B305"/>
     </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="2:2">
       <c r="B306"/>
     </row>
-    <row r="307" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="2:2">
       <c r="B307"/>
     </row>
-    <row r="308" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="2:2">
       <c r="B308"/>
     </row>
-    <row r="309" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="2:2">
       <c r="B309"/>
     </row>
-    <row r="310" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="2:2">
       <c r="B310"/>
     </row>
-    <row r="311" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="2:2">
       <c r="B311"/>
     </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="2:2">
       <c r="B312"/>
     </row>
-    <row r="313" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="2:2">
       <c r="B313"/>
     </row>
-    <row r="314" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="2:2">
       <c r="B314"/>
     </row>
-    <row r="315" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="2:2">
       <c r="B315"/>
     </row>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="2:2">
       <c r="B316"/>
     </row>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="2:2">
       <c r="B317"/>
     </row>
-    <row r="318" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="2:2">
       <c r="B318"/>
     </row>
-    <row r="319" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="2:2">
       <c r="B319"/>
     </row>
-    <row r="320" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="320" spans="2:2">
       <c r="B320"/>
     </row>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="321" spans="2:2">
       <c r="B321"/>
     </row>
-    <row r="322" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="2:2">
       <c r="B322"/>
     </row>
-    <row r="323" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="323" spans="2:2">
       <c r="B323"/>
     </row>
-    <row r="324" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="2:2">
       <c r="B324"/>
     </row>
-    <row r="325" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="2:2">
       <c r="B325"/>
     </row>
-    <row r="326" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="2:2">
       <c r="B326"/>
     </row>
-    <row r="327" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="2:2">
       <c r="B327"/>
     </row>
-    <row r="328" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="328" spans="2:2">
       <c r="B328"/>
     </row>
-    <row r="329" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="2:2">
       <c r="B329"/>
     </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="2:2">
       <c r="B330"/>
     </row>
-    <row r="331" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="2:2">
       <c r="B331"/>
     </row>
-    <row r="332" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="2:2">
       <c r="B332"/>
     </row>
-    <row r="333" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="2:2">
       <c r="B333"/>
     </row>
-    <row r="334" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="2:2">
       <c r="B334"/>
     </row>
-    <row r="335" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="2:2">
       <c r="B335"/>
     </row>
-    <row r="336" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="2:2">
       <c r="B336"/>
     </row>
-    <row r="337" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="337" spans="2:2">
       <c r="B337"/>
     </row>
-    <row r="338" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="2:2">
       <c r="B338"/>
     </row>
-    <row r="339" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="2:2">
       <c r="B339"/>
     </row>
-    <row r="340" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="2:2">
       <c r="B340"/>
     </row>
-    <row r="341" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="2:2">
       <c r="B341"/>
     </row>
-    <row r="342" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="2:2">
       <c r="B342"/>
     </row>
-    <row r="343" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="2:2">
       <c r="B343"/>
     </row>
-    <row r="344" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="2:2">
       <c r="B344"/>
     </row>
-    <row r="345" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="2:2">
       <c r="B345"/>
     </row>
-    <row r="346" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="2:2">
       <c r="B346"/>
     </row>
-    <row r="347" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="2:2">
       <c r="B347"/>
     </row>
-    <row r="348" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="2:2">
       <c r="B348"/>
     </row>
-    <row r="349" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="2:2">
       <c r="B349"/>
     </row>
-    <row r="350" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="2:2">
       <c r="B350"/>
     </row>
-    <row r="351" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="351" spans="2:2">
       <c r="B351"/>
     </row>
-    <row r="352" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="2:2">
       <c r="B352"/>
     </row>
-    <row r="353" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="2:2">
       <c r="B353"/>
     </row>
-    <row r="354" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="354" spans="2:2">
       <c r="B354"/>
     </row>
-    <row r="355" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="355" spans="2:2">
       <c r="B355"/>
     </row>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="2:2">
       <c r="B356"/>
     </row>
-    <row r="357" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="2:2">
       <c r="B357"/>
     </row>
-    <row r="358" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="358" spans="2:2">
       <c r="B358"/>
     </row>
-    <row r="359" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="359" spans="2:2">
       <c r="B359"/>
     </row>
-    <row r="360" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="360" spans="2:2">
       <c r="B360"/>
     </row>
-    <row r="361" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="2:2">
       <c r="B361"/>
     </row>
-    <row r="362" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="362" spans="2:2">
       <c r="B362"/>
     </row>
-    <row r="363" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="2:2">
       <c r="B363"/>
     </row>
-    <row r="364" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="364" spans="2:2">
       <c r="B364"/>
     </row>
-    <row r="365" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="2:2">
       <c r="B365"/>
     </row>
-    <row r="366" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="2:2">
       <c r="B366"/>
     </row>
-    <row r="367" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="367" spans="2:2">
       <c r="B367"/>
     </row>
-    <row r="368" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="368" spans="2:2">
       <c r="B368"/>
     </row>
-    <row r="369" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="369" spans="2:2">
       <c r="B369"/>
     </row>
-    <row r="370" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="2:2">
       <c r="B370"/>
     </row>
-    <row r="371" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="371" spans="2:2">
       <c r="B371"/>
     </row>
-    <row r="372" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="372" spans="2:2">
       <c r="B372"/>
     </row>
-    <row r="373" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="2:2">
       <c r="B373"/>
     </row>
-    <row r="374" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="2:2">
       <c r="B374"/>
     </row>
-    <row r="375" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="375" spans="2:2">
       <c r="B375"/>
     </row>
-    <row r="376" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="2:2">
       <c r="B376"/>
     </row>
-    <row r="377" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="2:2">
       <c r="B377"/>
     </row>
-    <row r="378" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="2:2">
       <c r="B378"/>
     </row>
-    <row r="379" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="2:2">
       <c r="B379"/>
     </row>
-    <row r="380" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="2:2">
       <c r="B380"/>
     </row>
-    <row r="381" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="381" spans="2:2">
       <c r="B381"/>
     </row>
-    <row r="382" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="382" spans="2:2">
       <c r="B382"/>
     </row>
-    <row r="383" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="2:2">
       <c r="B383"/>
     </row>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="2:2">
       <c r="B384"/>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="2:2">
       <c r="B385"/>
     </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="2:2">
       <c r="B386"/>
     </row>
-    <row r="387" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="387" spans="2:2">
       <c r="B387"/>
     </row>
-    <row r="388" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="2:2">
       <c r="B388"/>
     </row>
-    <row r="389" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="389" spans="2:2">
       <c r="B389"/>
     </row>
-    <row r="390" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="390" spans="2:2">
       <c r="B390"/>
     </row>
-    <row r="391" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="2:2">
       <c r="B391"/>
     </row>
-    <row r="392" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="2:2">
       <c r="B392"/>
     </row>
-    <row r="393" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="2:2">
       <c r="B393"/>
     </row>
-    <row r="394" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="2:2">
       <c r="B394"/>
     </row>
-    <row r="395" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="395" spans="2:2">
       <c r="B395"/>
     </row>
-    <row r="396" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="396" spans="2:2">
       <c r="B396"/>
     </row>
-    <row r="397" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="397" spans="2:2">
       <c r="B397"/>
     </row>
-    <row r="398" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="398" spans="2:2">
       <c r="B398"/>
     </row>
-    <row r="399" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="2:2">
       <c r="B399"/>
     </row>
-    <row r="400" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="2:2">
       <c r="B400"/>
     </row>
-    <row r="401" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="401" spans="2:2">
       <c r="B401"/>
     </row>
-    <row r="402" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="2:2">
       <c r="B402"/>
     </row>
-    <row r="403" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="403" spans="2:2">
       <c r="B403"/>
     </row>
-    <row r="404" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="404" spans="2:2">
       <c r="B404"/>
     </row>
-    <row r="405" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="2:2">
       <c r="B405"/>
     </row>
-    <row r="406" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="2:2">
       <c r="B406"/>
     </row>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="2:2">
       <c r="B407"/>
     </row>
-    <row r="408" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="408" spans="2:2">
       <c r="B408"/>
     </row>
-    <row r="409" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="409" spans="2:2">
       <c r="B409"/>
     </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="2:2">
       <c r="B410"/>
     </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="2:2">
       <c r="B411"/>
     </row>
-    <row r="412" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="412" spans="2:2">
       <c r="B412"/>
     </row>
-    <row r="413" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="413" spans="2:2">
       <c r="B413"/>
     </row>
-    <row r="414" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="414" spans="2:2">
       <c r="B414"/>
     </row>
-    <row r="415" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="415" spans="2:2">
       <c r="B415"/>
     </row>
-    <row r="416" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="416" spans="2:2">
       <c r="B416"/>
     </row>
-    <row r="417" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="417" spans="2:2">
       <c r="B417"/>
     </row>
-    <row r="418" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="418" spans="2:2">
       <c r="B418"/>
     </row>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="2:2">
       <c r="B419"/>
     </row>
-    <row r="420" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="2:2">
       <c r="B420"/>
     </row>
-    <row r="421" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="2:2">
       <c r="B421"/>
     </row>
-    <row r="422" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="422" spans="2:2">
       <c r="B422"/>
     </row>
-    <row r="423" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="423" spans="2:2">
       <c r="B423"/>
     </row>
-    <row r="424" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="424" spans="2:2">
       <c r="B424"/>
     </row>
-    <row r="425" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="425" spans="2:2">
       <c r="B425"/>
     </row>
-    <row r="426" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="426" spans="2:2">
       <c r="B426"/>
     </row>
-    <row r="427" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="427" spans="2:2">
       <c r="B427"/>
     </row>
-    <row r="428" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="428" spans="2:2">
       <c r="B428"/>
     </row>
-    <row r="429" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="429" spans="2:2">
       <c r="B429"/>
     </row>
-    <row r="430" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="430" spans="2:2">
       <c r="B430"/>
     </row>
-    <row r="431" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="431" spans="2:2">
       <c r="B431"/>
     </row>
-    <row r="432" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="432" spans="2:2">
       <c r="B432"/>
     </row>
-    <row r="433" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="433" spans="2:2">
       <c r="B433"/>
     </row>
-    <row r="434" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="434" spans="2:2">
       <c r="B434"/>
     </row>
-    <row r="435" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="435" spans="2:2">
       <c r="B435"/>
     </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="2:2">
       <c r="B436"/>
     </row>
-    <row r="437" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="437" spans="2:2">
       <c r="B437"/>
     </row>
-    <row r="438" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="438" spans="2:2">
       <c r="B438"/>
     </row>
-    <row r="439" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="439" spans="2:2">
       <c r="B439"/>
     </row>
-    <row r="440" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="440" spans="2:2">
       <c r="B440"/>
     </row>
-    <row r="441" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="441" spans="2:2">
       <c r="B441"/>
     </row>
-    <row r="442" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="442" spans="2:2">
       <c r="B442"/>
     </row>
-    <row r="443" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="443" spans="2:2">
       <c r="B443"/>
     </row>
-    <row r="444" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="444" spans="2:2">
       <c r="B444"/>
     </row>
-    <row r="445" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="445" spans="2:2">
       <c r="B445"/>
     </row>
-    <row r="446" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="446" spans="2:2">
       <c r="B446"/>
     </row>
-    <row r="447" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="447" spans="2:2">
       <c r="B447"/>
     </row>
-    <row r="448" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="448" spans="2:2">
       <c r="B448"/>
     </row>
-    <row r="449" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="449" spans="2:2">
       <c r="B449"/>
     </row>
-    <row r="450" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="450" spans="2:2">
       <c r="B450"/>
     </row>
-    <row r="451" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="451" spans="2:2">
       <c r="B451"/>
     </row>
-    <row r="452" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="452" spans="2:2">
       <c r="B452"/>
     </row>
-    <row r="453" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="453" spans="2:2">
       <c r="B453"/>
     </row>
-    <row r="454" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="454" spans="2:2">
       <c r="B454"/>
     </row>
-    <row r="455" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="455" spans="2:2">
       <c r="B455"/>
     </row>
-    <row r="456" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="456" spans="2:2">
       <c r="B456"/>
     </row>
-    <row r="457" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="457" spans="2:2">
       <c r="B457"/>
     </row>
-    <row r="458" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="458" spans="2:2">
       <c r="B458"/>
     </row>
-    <row r="459" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="459" spans="2:2">
       <c r="B459"/>
     </row>
-    <row r="460" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="460" spans="2:2">
       <c r="B460"/>
     </row>
-    <row r="461" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="461" spans="2:2">
       <c r="B461"/>
     </row>
-    <row r="462" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="462" spans="2:2">
       <c r="B462"/>
     </row>
-    <row r="463" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="463" spans="2:2">
       <c r="B463"/>
     </row>
-    <row r="464" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="464" spans="2:2">
       <c r="B464"/>
     </row>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="2:2">
       <c r="B465"/>
     </row>
-    <row r="466" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="466" spans="2:2">
       <c r="B466"/>
     </row>
-    <row r="467" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="467" spans="2:2">
       <c r="B467"/>
     </row>
-    <row r="468" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="468" spans="2:2">
       <c r="B468"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="2:2">
       <c r="B469"/>
     </row>
-    <row r="470" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="470" spans="2:2">
       <c r="B470"/>
     </row>
-    <row r="471" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="471" spans="2:2">
       <c r="B471"/>
     </row>
-    <row r="472" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="472" spans="2:2">
       <c r="B472"/>
     </row>
-    <row r="473" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="473" spans="2:2">
       <c r="B473"/>
     </row>
-    <row r="474" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="474" spans="2:2">
       <c r="B474"/>
     </row>
-    <row r="475" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="475" spans="2:2">
       <c r="B475"/>
     </row>
-    <row r="476" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="476" spans="2:2">
       <c r="B476"/>
     </row>
-    <row r="477" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="477" spans="2:2">
       <c r="B477"/>
     </row>
-    <row r="478" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="478" spans="2:2">
       <c r="B478"/>
     </row>
-    <row r="479" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="479" spans="2:2">
       <c r="B479"/>
     </row>
-    <row r="480" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="480" spans="2:2">
       <c r="B480"/>
     </row>
-    <row r="481" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="481" spans="2:2">
       <c r="B481"/>
     </row>
-    <row r="482" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="482" spans="2:2">
       <c r="B482"/>
     </row>
-    <row r="483" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="483" spans="2:2">
       <c r="B483"/>
     </row>
-    <row r="484" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="484" spans="2:2">
       <c r="B484"/>
     </row>
-    <row r="485" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="485" spans="2:2">
       <c r="B485"/>
     </row>
-    <row r="486" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="486" spans="2:2">
       <c r="B486"/>
     </row>
-    <row r="487" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="487" spans="2:2">
       <c r="B487"/>
     </row>
-    <row r="488" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="488" spans="2:2">
       <c r="B488"/>
     </row>
-    <row r="489" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="489" spans="2:2">
       <c r="B489"/>
     </row>
-    <row r="490" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="490" spans="2:2">
       <c r="B490"/>
     </row>
-    <row r="491" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="491" spans="2:2">
       <c r="B491"/>
     </row>
-    <row r="492" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="492" spans="2:2">
       <c r="B492"/>
     </row>
-    <row r="493" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="493" spans="2:2">
       <c r="B493"/>
     </row>
-    <row r="494" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="494" spans="2:2">
       <c r="B494"/>
     </row>
-    <row r="495" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="495" spans="2:2">
       <c r="B495"/>
     </row>
-    <row r="496" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="496" spans="2:2">
       <c r="B496"/>
     </row>
-    <row r="497" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="497" spans="2:2">
       <c r="B497"/>
     </row>
-    <row r="498" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="498" spans="2:2">
       <c r="B498"/>
     </row>
-    <row r="499" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="499" spans="2:2">
       <c r="B499"/>
     </row>
-    <row r="500" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="500" spans="2:2">
       <c r="B500"/>
     </row>
-    <row r="501" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="501" spans="2:2">
       <c r="B501"/>
     </row>
   </sheetData>

--- a/CWatM_settings/cwatm_settings.xlsx
+++ b/CWatM_settings/cwatm_settings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaumot\Documents\GitHub\FUSE\CWatM_settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B2385E-5FDF-49D2-8F3B-F5CA5DC3A831}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11B92DF-83BB-4597-84C4-2ABE676FAD4F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{3B47940C-5F20-42D1-80D0-733DA86DBAA8}"/>
+    <workbookView xWindow="2562" yWindow="2562" windowWidth="17280" windowHeight="8994" xr2:uid="{3B47940C-5F20-42D1-80D0-733DA86DBAA8}"/>
   </bookViews>
   <sheets>
     <sheet name="CWatM_input" sheetId="3" r:id="rId1"/>
@@ -1974,7 +1974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2090,6 +2090,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2441,8 +2444,8 @@
       <c r="A4" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="38">
-        <v>35</v>
+      <c r="B4" s="46">
+        <v>4748</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2450,7 +2453,7 @@
         <v>407</v>
       </c>
       <c r="B5" s="39">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/CWatM_settings/cwatm_settings.xlsx
+++ b/CWatM_settings/cwatm_settings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaumot\Documents\GitHub\FUSE\CWatM_settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11B92DF-83BB-4597-84C4-2ABE676FAD4F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDBA13E-AC64-4BB3-B064-B1E0E3A38A09}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2562" yWindow="2562" windowWidth="17280" windowHeight="8994" xr2:uid="{3B47940C-5F20-42D1-80D0-733DA86DBAA8}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{3B47940C-5F20-42D1-80D0-733DA86DBAA8}"/>
   </bookViews>
   <sheets>
     <sheet name="CWatM_input" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="571">
   <si>
     <t>PathRoot</t>
   </si>
@@ -1737,6 +1737,15 @@
   </si>
   <si>
     <t>OUT_MAP_totalend</t>
+  </si>
+  <si>
+    <t>discharge, lakeResInflowDis, lakeResOutflowDis, lakeResStorage, act_bigLakeResAbst_alloc</t>
+  </si>
+  <si>
+    <t>0.00005</t>
+  </si>
+  <si>
+    <t>0.05</t>
   </si>
 </sst>
 </file>
@@ -2445,7 +2454,7 @@
         <v>126</v>
       </c>
       <c r="B4" s="46">
-        <v>4748</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2453,7 +2462,7 @@
         <v>407</v>
       </c>
       <c r="B5" s="39">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2468,7 +2477,9 @@
       <c r="A7" s="27" t="s">
         <v>544</v>
       </c>
-      <c r="B7" s="39"/>
+      <c r="B7" s="39" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="27" t="s">
@@ -2575,12 +2586,36 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25"/>
+      <c r="A21" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
+      <c r="A22" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>570</v>
+      </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="25"/>

--- a/CWatM_settings/cwatm_settings.xlsx
+++ b/CWatM_settings/cwatm_settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillaumot\Documents\GitHub\FUSE\CWatM_settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDBA13E-AC64-4BB3-B064-B1E0E3A38A09}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3644AE-0DAC-4236-A9F0-BAA500E73048}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{3B47940C-5F20-42D1-80D0-733DA86DBAA8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="571">
   <si>
     <t>PathRoot</t>
   </si>
@@ -1715,9 +1715,6 @@
     <t xml:space="preserve"> $(FILE_PATHS:PathMaps)/init/Nira</t>
   </si>
   <si>
-    <t xml:space="preserve"> 01/01/1995</t>
-  </si>
-  <si>
     <t>modflowWaterLevel</t>
   </si>
   <si>
@@ -1742,10 +1739,13 @@
     <t>discharge, lakeResInflowDis, lakeResOutflowDis, lakeResStorage, act_bigLakeResAbst_alloc</t>
   </si>
   <si>
-    <t>0.00005</t>
-  </si>
-  <si>
     <t>0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01/01/1987</t>
+  </si>
+  <si>
+    <t>0.000005</t>
   </si>
 </sst>
 </file>
@@ -2438,7 +2438,7 @@
         <v>123</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2454,7 +2454,7 @@
         <v>126</v>
       </c>
       <c r="B4" s="46">
-        <v>10</v>
+        <v>7665</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2462,7 +2462,7 @@
         <v>407</v>
       </c>
       <c r="B5" s="39">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2478,7 +2478,7 @@
         <v>544</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2486,7 +2486,7 @@
         <v>517</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2494,7 +2494,7 @@
         <v>100</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.7" thickBot="1">
@@ -2502,7 +2502,7 @@
         <v>101</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2518,7 +2518,7 @@
         <v>117</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2574,15 +2574,15 @@
         <v>131</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="45" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2597,8 +2597,8 @@
       <c r="A22" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>77</v>
+      <c r="B22" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2606,7 +2606,7 @@
         <v>132</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2614,7 +2614,7 @@
         <v>551</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27" spans="1:2">
